--- a/rules/CORE-000031/negative/02/data/unit-test-coreid-CG0659-negative 2.xlsx
+++ b/rules/CORE-000031/negative/02/data/unit-test-coreid-CG0659-negative 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marisa_wyckmans\CORE\CDISC_Rule_Authoring\core-contributor\rules\CORE-000031\negative\02\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4211E0-FB45-474F-A5C6-A5AD008A8505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3965AD-E372-4634-8870-AB23B3B9209C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -236,7 +236,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,6 +252,11 @@
     </font>
     <font>
       <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -306,7 +311,6 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -320,6 +324,7 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -629,10 +634,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
@@ -648,7 +653,7 @@
       <c r="A3" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>68</v>
       </c>
     </row>
@@ -663,10 +668,10 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -687,24 +692,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -739,283 +747,283 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:18" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="R1" s="6" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="2" spans="1:18" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R2" s="3" t="s">
-        <v>49</v>
-      </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="A3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J3" s="3" t="s">
+      <c r="E3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L3" s="3" t="s">
+      <c r="K3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="P3" s="3" t="s">
+      <c r="M3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Q3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="R3" s="3" t="s">
+      <c r="Q3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>12</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>4</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>8</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>8</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>7</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>40</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>5</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <v>23</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <v>20</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <v>8</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="2">
         <v>1</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <v>8</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="2">
         <v>200</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="2">
         <v>9</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O4" s="2">
         <v>10</v>
       </c>
-      <c r="P4" s="3">
+      <c r="P4" s="2">
         <v>8</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="Q4" s="2">
+        <v>200</v>
+      </c>
+      <c r="R4" s="2">
         <v>19</v>
       </c>
-      <c r="R4" s="3">
-        <v>200</v>
-      </c>
     </row>
     <row r="5" spans="1:18" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="3">
         <v>1</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="3">
         <v>3</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="P5" s="4">
+      <c r="P5" s="3">
         <v>1</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="R5" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/rules/CORE-000031/negative/02/data/unit-test-coreid-CG0659-negative 2.xlsx
+++ b/rules/CORE-000031/negative/02/data/unit-test-coreid-CG0659-negative 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marisa_wyckmans\CORE\CDISC_Rule_Authoring\core-contributor\rules\CORE-000031\negative\02\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3965AD-E372-4634-8870-AB23B3B9209C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3292830B-5D19-4803-90A6-B4BC3C6E9008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -229,7 +229,7 @@
     <t>sdtmct</t>
   </si>
   <si>
-    <t>2026-03-27</t>
+    <t>2025-03-28</t>
   </si>
 </sst>
 </file>
